--- a/data/trans_orig/IQ3001_MoAR-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IQ3001_MoAR-Clase-trans_orig.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Meses en la que empezaron a comer cereales sin gluten</t>
+          <t>Meses en la que empezaron a comer cereales sin gluten (tasa de respuesta: 64,38%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,13; 5,41</t>
+          <t>4,1; 5,34</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,34; 7,04</t>
+          <t>5,34; 6,85</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,4; 5,32</t>
+          <t>4,38; 5,33</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,7; 4,6</t>
+          <t>3,65; 4,68</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,32; 5,17</t>
+          <t>4,36; 5,14</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,88; 7,49</t>
+          <t>4,83; 7,53</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,05; 4,85</t>
+          <t>4,03; 4,84</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,92; 5,78</t>
+          <t>4,89; 5,82</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,8; 6,15</t>
+          <t>4,83; 6,19</t>
         </is>
       </c>
     </row>
@@ -787,47 +787,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,77; 5,18</t>
+          <t>3,86; 5,18</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,93; 6,22</t>
+          <t>4,94; 6,22</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,64; 5,79</t>
+          <t>4,67; 5,86</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,39; 5,59</t>
+          <t>4,37; 5,52</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,21; 5,04</t>
+          <t>4,23; 5,07</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,8; 6,45</t>
+          <t>4,81; 6,5</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,39; 5,35</t>
+          <t>4,3; 5,26</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,66; 5,46</t>
+          <t>4,68; 5,5</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,9; 5,92</t>
+          <t>4,94; 5,95</t>
         </is>
       </c>
     </row>
@@ -897,47 +897,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,84; 4,47</t>
+          <t>3,84; 4,4</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,73; 6,06</t>
+          <t>4,77; 6,04</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,92; 7,61</t>
+          <t>4,89; 7,46</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,13; 8,15</t>
+          <t>4,22; 7,9</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,16; 5,1</t>
+          <t>4,13; 5,08</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,35; 7,33</t>
+          <t>4,31; 7,37</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,17; 6,86</t>
+          <t>4,16; 6,51</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,52; 5,29</t>
+          <t>4,48; 5,32</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,86; 6,91</t>
+          <t>4,92; 6,95</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1007,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,93; 4,93</t>
+          <t>3,87; 4,9</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,43; 5,41</t>
+          <t>4,44; 5,47</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,33; 7,15</t>
+          <t>5,35; 7,15</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,72; 4,69</t>
+          <t>3,68; 4,66</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,96; 6,0</t>
+          <t>4,95; 5,95</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,94; 6,64</t>
+          <t>4,91; 6,73</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,96; 4,66</t>
+          <t>3,97; 4,63</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,81; 5,52</t>
+          <t>4,77; 5,5</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,27; 6,57</t>
+          <t>5,3; 6,59</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1117,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,81; 5,17</t>
+          <t>3,8; 5,1</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,58; 5,81</t>
+          <t>4,59; 5,92</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,66; 8,06</t>
+          <t>5,69; 8,13</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,54; 4,72</t>
+          <t>3,48; 4,7</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,82; 6,96</t>
+          <t>4,85; 7,04</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,89; 6,71</t>
+          <t>4,82; 6,58</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,78; 4,68</t>
+          <t>3,79; 4,66</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,77; 5,97</t>
+          <t>4,85; 6,05</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,45; 6,93</t>
+          <t>5,46; 6,94</t>
         </is>
       </c>
     </row>
@@ -1227,47 +1227,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4,21; 5,95</t>
+          <t>4,12; 5,94</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4,02; 6,05</t>
+          <t>3,99; 5,94</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4,53; 6,72</t>
+          <t>4,6; 6,78</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4,29; 6,54</t>
+          <t>4,08; 6,47</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4,66; 6,01</t>
+          <t>4,64; 6,01</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4,16; 5,44</t>
+          <t>4,19; 5,45</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,52; 6,02</t>
+          <t>4,51; 6,0</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4,53; 5,74</t>
+          <t>4,57; 5,75</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4,6; 5,82</t>
+          <t>4,61; 5,87</t>
         </is>
       </c>
     </row>
@@ -1337,47 +1337,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,22; 4,73</t>
+          <t>4,23; 4,74</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4,91; 5,45</t>
+          <t>4,92; 5,49</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5,33; 6,14</t>
+          <t>5,34; 6,21</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,33; 5,02</t>
+          <t>4,33; 5,01</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,84; 5,37</t>
+          <t>4,85; 5,37</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,16; 5,95</t>
+          <t>5,12; 5,95</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,36; 4,8</t>
+          <t>4,37; 4,77</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,93; 5,3</t>
+          <t>4,94; 5,32</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5,32; 5,91</t>
+          <t>5,31; 5,9</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ3001_MoAR-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IQ3001_MoAR-Clase-trans_orig.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,1; 5,34</t>
+          <t>4,08; 5,37</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,34; 6,85</t>
+          <t>5,31; 6,89</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,38; 5,33</t>
+          <t>4,43; 5,31</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,65; 4,68</t>
+          <t>3,69; 4,65</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,36; 5,14</t>
+          <t>4,31; 5,13</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,83; 7,53</t>
+          <t>4,8; 7,61</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,03; 4,84</t>
+          <t>4,04; 4,89</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,89; 5,82</t>
+          <t>4,91; 5,82</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,83; 6,19</t>
+          <t>4,82; 6,36</t>
         </is>
       </c>
     </row>
@@ -787,47 +787,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,86; 5,18</t>
+          <t>3,79; 5,09</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,94; 6,22</t>
+          <t>4,9; 6,24</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,67; 5,86</t>
+          <t>4,68; 5,83</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,37; 5,52</t>
+          <t>4,4; 5,62</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,23; 5,07</t>
+          <t>4,21; 5,06</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,81; 6,5</t>
+          <t>4,89; 6,57</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,3; 5,26</t>
+          <t>4,31; 5,26</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,68; 5,5</t>
+          <t>4,62; 5,48</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,94; 5,95</t>
+          <t>4,92; 5,89</t>
         </is>
       </c>
     </row>
@@ -897,12 +897,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,84; 4,4</t>
+          <t>3,84; 4,41</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,77; 6,04</t>
+          <t>4,75; 6,07</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -912,22 +912,22 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,22; 7,9</t>
+          <t>4,18; 7,91</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,13; 5,08</t>
+          <t>4,17; 5,14</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,31; 7,37</t>
+          <t>4,31; 7,38</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,16; 6,51</t>
+          <t>4,14; 6,38</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,92; 6,95</t>
+          <t>4,87; 6,92</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1007,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,87; 4,9</t>
+          <t>3,79; 4,91</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,44; 5,47</t>
+          <t>4,47; 5,58</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,35; 7,15</t>
+          <t>5,32; 7,11</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,68; 4,66</t>
+          <t>3,72; 4,67</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,95; 5,95</t>
+          <t>4,97; 5,93</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,91; 6,73</t>
+          <t>4,97; 6,75</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,97; 4,63</t>
+          <t>3,96; 4,64</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,77; 5,5</t>
+          <t>4,83; 5,51</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,3; 6,59</t>
+          <t>5,28; 6,43</t>
         </is>
       </c>
     </row>
@@ -1117,12 +1117,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,8; 5,1</t>
+          <t>3,82; 5,26</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,59; 5,92</t>
+          <t>4,53; 5,86</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1132,32 +1132,32 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,48; 4,7</t>
+          <t>3,57; 4,77</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,85; 7,04</t>
+          <t>4,84; 6,95</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,82; 6,58</t>
+          <t>4,83; 6,77</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,79; 4,66</t>
+          <t>3,78; 4,68</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,85; 6,05</t>
+          <t>4,87; 6,01</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,46; 6,94</t>
+          <t>5,48; 6,91</t>
         </is>
       </c>
     </row>
@@ -1227,12 +1227,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4,12; 5,94</t>
+          <t>4,15; 5,96</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3,99; 5,94</t>
+          <t>3,95; 6,06</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1242,32 +1242,32 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4,08; 6,47</t>
+          <t>4,27; 6,53</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4,64; 6,01</t>
+          <t>4,6; 5,95</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4,19; 5,45</t>
+          <t>4,13; 5,4</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,51; 6,0</t>
+          <t>4,5; 5,97</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4,57; 5,75</t>
+          <t>4,55; 5,71</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4,61; 5,87</t>
+          <t>4,55; 5,88</t>
         </is>
       </c>
     </row>
@@ -1337,47 +1337,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,23; 4,74</t>
+          <t>4,24; 4,73</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4,92; 5,49</t>
+          <t>4,93; 5,47</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5,34; 6,21</t>
+          <t>5,36; 6,17</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,33; 5,01</t>
+          <t>4,33; 4,99</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,85; 5,37</t>
+          <t>4,84; 5,39</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,12; 5,95</t>
+          <t>5,16; 5,99</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,37; 4,77</t>
+          <t>4,35; 4,82</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,94; 5,32</t>
+          <t>4,95; 5,32</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5,31; 5,9</t>
+          <t>5,34; 5,91</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ3001_MoAR-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IQ3001_MoAR-Clase-trans_orig.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>4,14</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>4,75</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>5,74</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>4,64</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>5,77</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>4,88</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4,14</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>4,75</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>5,74</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,08; 5,37</t>
+          <t>3,7; 4,6</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,31; 6,89</t>
+          <t>4,32; 5,17</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,43; 5,31</t>
+          <t>4,88; 7,49</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,69; 4,65</t>
+          <t>4,13; 5,41</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,31; 5,13</t>
+          <t>5,34; 7,04</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,8; 7,61</t>
+          <t>4,4; 5,32</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,04; 4,89</t>
+          <t>4,05; 4,85</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,91; 5,82</t>
+          <t>4,92; 5,78</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,82; 6,36</t>
+          <t>4,8; 6,15</t>
         </is>
       </c>
     </row>
@@ -734,32 +734,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>4,96</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>4,61</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>5,52</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>4,45</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>5,53</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>5,18</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>4,96</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>4,61</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>5,52</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -787,47 +787,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,79; 5,09</t>
+          <t>4,39; 5,59</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,9; 6,24</t>
+          <t>4,21; 5,04</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,68; 5,83</t>
+          <t>4,8; 6,45</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,4; 5,62</t>
+          <t>3,77; 5,18</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,21; 5,06</t>
+          <t>4,93; 6,22</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,89; 6,57</t>
+          <t>4,64; 5,79</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,31; 5,26</t>
+          <t>4,39; 5,35</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,62; 5,48</t>
+          <t>4,66; 5,46</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,92; 5,89</t>
+          <t>4,9; 5,92</t>
         </is>
       </c>
     </row>
@@ -844,32 +844,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>5,34</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>4,55</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>5,39</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>4,15</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>5,29</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>6,08</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>5,34</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>4,55</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>5,39</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -897,47 +897,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,84; 4,41</t>
+          <t>4,13; 8,15</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,75; 6,07</t>
+          <t>4,16; 5,1</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,89; 7,46</t>
+          <t>4,35; 7,33</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,18; 7,91</t>
+          <t>3,84; 4,47</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,17; 5,14</t>
+          <t>4,73; 6,06</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,31; 7,38</t>
+          <t>4,92; 7,61</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,14; 6,38</t>
+          <t>4,17; 6,86</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,48; 5,32</t>
+          <t>4,52; 5,29</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,87; 6,92</t>
+          <t>4,86; 6,91</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>4,15</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>5,37</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>5,59</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>4,45</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>4,85</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>5,96</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4,15</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>5,37</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>5,59</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1007,47 +1007,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,79; 4,91</t>
+          <t>3,72; 4,69</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,47; 5,58</t>
+          <t>4,96; 6,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,32; 7,11</t>
+          <t>4,94; 6,64</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,72; 4,67</t>
+          <t>3,93; 4,93</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,97; 5,93</t>
+          <t>4,43; 5,41</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,97; 6,75</t>
+          <t>5,33; 7,15</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,96; 4,64</t>
+          <t>3,96; 4,66</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,83; 5,51</t>
+          <t>4,81; 5,52</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,28; 6,43</t>
+          <t>5,27; 6,57</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>4,19</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>5,58</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>5,6</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>4,23</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>5,1</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>6,64</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>4,19</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>5,58</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>5,6</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1117,32 +1117,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,82; 5,26</t>
+          <t>3,54; 4,72</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,53; 5,86</t>
+          <t>4,82; 6,96</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,69; 8,13</t>
+          <t>4,89; 6,71</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,57; 4,77</t>
+          <t>3,81; 5,17</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,84; 6,95</t>
+          <t>4,58; 5,81</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,83; 6,77</t>
+          <t>5,66; 8,06</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1152,12 +1152,12 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,87; 6,01</t>
+          <t>4,77; 5,97</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,48; 6,91</t>
+          <t>5,45; 6,93</t>
         </is>
       </c>
     </row>
@@ -1174,32 +1174,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>5,58</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>5,22</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>4,84</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>4,9</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>4,93</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>5,42</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>5,58</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>5,22</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>4,84</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1227,47 +1227,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4,15; 5,96</t>
+          <t>4,29; 6,54</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3,95; 6,06</t>
+          <t>4,66; 6,01</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4,6; 6,78</t>
+          <t>4,16; 5,44</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4,27; 6,53</t>
+          <t>4,21; 5,95</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4,6; 5,95</t>
+          <t>4,02; 6,05</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4,13; 5,4</t>
+          <t>4,53; 6,72</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,5; 5,97</t>
+          <t>4,52; 6,02</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4,55; 5,71</t>
+          <t>4,53; 5,74</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4,55; 5,88</t>
+          <t>4,6; 5,82</t>
         </is>
       </c>
     </row>
@@ -1284,32 +1284,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>4,62</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>5,07</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>5,51</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>4,48</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>5,17</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>5,68</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>4,62</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>5,07</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>5,51</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1337,47 +1337,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,24; 4,73</t>
+          <t>4,33; 5,02</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4,93; 5,47</t>
+          <t>4,84; 5,37</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5,36; 6,17</t>
+          <t>5,16; 5,95</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,33; 4,99</t>
+          <t>4,22; 4,73</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,84; 5,39</t>
+          <t>4,91; 5,45</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,16; 5,99</t>
+          <t>5,33; 6,14</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,35; 4,82</t>
+          <t>4,36; 4,8</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,95; 5,32</t>
+          <t>4,93; 5,3</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5,34; 5,91</t>
+          <t>5,32; 5,91</t>
         </is>
       </c>
     </row>
